--- a/Data/BloodRelation.xlsx
+++ b/Data/BloodRelation.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,216 +472,216 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>Both are parents-in-law of a married couple.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>P is R’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -691,197 +691,197 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>R is P’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>R is S’s brother → T’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>A is C’s son.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -891,49 +891,49 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>L is M’s father.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -946,13 +946,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -992,226 +992,226 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>Arjun is Kiran’s father.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>A is C’s sister.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1221,98 +1221,98 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>S is Q’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1352,56 +1352,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>T’s sister is V → U is her nephew → V is aunt.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1416,232 +1416,232 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>T is K’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Meera is Ravi’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>A is also D’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Sister of husband → sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>A's mother is B's daughter. How is B related to A?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1656,27 +1656,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1706,133 +1706,133 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>A is also C’s son.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>P is R’s brother as he is Q’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1872,68 +1872,68 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -1946,62 +1946,62 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Son’s mother is wife → her brother is brother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2011,72 +2011,72 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>B is N’s brother → he is D’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>A is the son of B’s son. How is A related to B?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>A is B’s grandson.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2106,177 +2106,177 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>C is A’s grandparent.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grandfather</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>Raj is Meena’s father.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2306,53 +2306,53 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>N’s sister is M → M is O’s sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2392,11 +2392,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2406,19 +2406,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -2426,32 +2426,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2461,27 +2461,27 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A's mother is B's daughter. How is B related to A?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2496,72 +2496,72 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
+          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Granddaughter</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Daughter</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Niece</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
+          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
+          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2581,382 +2581,382 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
+          <t>Meena is Sneha’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
+          <t>A's father is B. C is B's sister. How is C related to A?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Father’s sister’s son is a cousin.</t>
+          <t>C is A’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
+          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>R is T’s grandfather through M.</t>
+          <t>The man’s sister is Maya herself → he is her brother.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>N is M’s brother, so he is P’s maternal uncle.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
+          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Z is X’s uncle as he is Y’s brother.</t>
+          <t>F is D’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
+          <t>G is the only daughter of H’s only son. How is G related to H?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Reena is Rahul’s mother too.</t>
+          <t>Only son’s daughter is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
+          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
+          <t>Reena is Rahul’s mother too.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>A is also D’s daughter.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
+          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>The man is the brother of Suman’s husband → he is uncle.</t>
+          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2966,19 +2966,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -2986,72 +2986,72 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>P is R’s brother as he is Q’s maternal uncle.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
+          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>N’s sister is M → M is O’s sister-in-law.</t>
+          <t>Father’s sister’s son is a cousin.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A's father is B. C is B's sister. How is C related to A?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3061,77 +3061,77 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C is A’s aunt.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C is A’s grandparent.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3141,252 +3141,252 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Father’s daughter is Lata herself → boy is her son.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Z is X’s child.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
+          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Grandfather</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>B is N’s brother → he is D’s maternal uncle.</t>
+          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>A is also C’s son.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Ravi is Tina’s uncle.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Arjun is Kiran’s father.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Meena is Sneha’s mother-in-law.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
@@ -3432,146 +3432,146 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Meera is Ravi’s grandmother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
+          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Mother’s sister’s husband is uncle.</t>
+          <t>M is the grandmother of O.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
+          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Both are parents-in-law of a married couple.</t>
+          <t>N is M’s brother, so he is P’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3581,77 +3581,77 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Son’s mother is wife → her brother is brother-in-law.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Raj is Meena’s father.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
+          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3661,107 +3661,107 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>S is Q’s grandfather.</t>
+          <t>Father’s daughter is Lata herself → boy is her son.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
+          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>T’s sister is V → U is her nephew → V is aunt.</t>
+          <t>R is T’s grandfather through M.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3771,112 +3771,112 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>R is S’s brother → T’s uncle.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>P is R’s mother-in-law.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
+          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M is the grandmother of O.</t>
+          <t>Z is X’s uncle as he is Y’s brother.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3906,67 +3906,67 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>The man’s sister is Maya herself → he is her brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
+          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
+          <t>Mother’s sister’s husband is uncle.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3976,237 +3976,237 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>Husband</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>A is C’s sister.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
+          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>P is Q’s brother → R’s maternal uncle.</t>
+          <t>Z is X’s child.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>A is C’s son.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>F is D’s grandmother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sister of husband → sister-in-law.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>G is the only daughter of H’s only son. How is G related to H?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4216,162 +4216,162 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Only son’s daughter is granddaughter.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
+          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L is M’s father.</t>
+          <t>Ravi is Tina’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>A is the son of B’s son. How is A related to B?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>A is B’s grandson.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
+          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>Grandfather</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4381,27 +4381,27 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>R is P’s grandfather.</t>
+          <t>P is Q’s brother → R’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
+          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>T is K’s grandfather.</t>
+          <t>The man is the brother of Suman’s husband → he is uncle.</t>
         </is>
       </c>
     </row>

--- a/Data/BloodRelation.xlsx
+++ b/Data/BloodRelation.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,87 +491,87 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man is the brother of Suman’s husband → he is uncle.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -581,178 +581,178 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>P is Q’s brother → R’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Both are parents-in-law of a married couple.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P is R’s mother-in-law.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
+          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Grandfather</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R is P’s grandfather.</t>
+          <t>Ravi is Tina’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R is S’s brother → T’s uncle.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -792,101 +792,101 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A is C’s son.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -896,322 +896,322 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L is M’s father.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Z is X’s child.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Arjun is Kiran’s father.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
+          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>A is C’s sister.</t>
+          <t>Mother’s sister’s husband is uncle.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
+          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
+          <t>Z is X’s uncle as he is Y’s brother.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1221,27 +1221,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1251,348 +1251,348 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>R is T’s grandfather through M.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>S is Q’s grandfather.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Father’s daughter is Lata herself → boy is her son.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>T’s sister is V → U is her nephew → V is aunt.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>T is K’s grandfather.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
+          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Meera is Ravi’s grandmother.</t>
+          <t>N is M’s brother, so he is P’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>M is the grandmother of O.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>A is also D’s daughter.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
+          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sister of husband → sister-in-law.</t>
+          <t>She is referring to herself.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A's mother is B's daughter. How is B related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1661,178 +1661,178 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>A is also C’s son.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
+          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P is R’s brother as he is Q’s maternal uncle.</t>
+          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1872,96 +1872,96 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
+          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1976,97 +1976,97 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Son’s mother is wife → her brother is brother-in-law.</t>
+          <t>Father’s sister’s son is a cousin.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>B is N’s brother → he is D’s maternal uncle.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A is the son of B’s son. How is A related to B?</t>
+          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A is B’s grandson.</t>
+          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
         </is>
       </c>
     </row>
@@ -2112,16 +2112,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
+          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2131,152 +2131,152 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C is A’s grandparent.</t>
+          <t>Reena is Rahul’s mother too.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
+          <t>G is the only daughter of H’s only son. How is G related to H?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Daughter</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
+          <t>Only son’s daughter is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
+          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Raj is Meena’s father.</t>
+          <t>F is D’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2286,19 +2286,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -2306,107 +2306,107 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man’s sister is Maya herself → he is her brother.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>N’s sister is M → M is O’s sister-in-law.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A's father is B. C is B's sister. How is C related to A?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>C is A’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2416,157 +2416,157 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Meena is Sneha’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2576,42 +2576,42 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Meena is Sneha’s mother-in-law.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A's father is B. C is B's sister. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2621,62 +2621,62 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C is A’s aunt.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>N’s sister is M → M is O’s sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2706,142 +2706,142 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>The man’s sister is Maya herself → he is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
+          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>F is D’s grandmother.</t>
+          <t>Raj is Meena’s father.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>G is the only daughter of H’s only son. How is G related to H?</t>
+          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Only son’s daughter is granddaughter.</t>
+          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
+          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2851,157 +2851,157 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Reena is Rahul’s mother too.</t>
+          <t>C is A’s grandparent.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>S is Q’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
+          <t>A is the son of B’s son. How is A related to B?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
+          <t>A is B’s grandson.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>B is N’s brother → he is D’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
+          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3016,44 +3016,44 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Father’s sister’s son is a cousin.</t>
+          <t>Son’s mother is wife → her brother is brother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -3066,53 +3066,53 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3152,141 +3152,141 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
+          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
+          <t>P is R’s brother as he is Q’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>A is also C’s son.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3296,44 +3296,44 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>L is M’s father.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A's mother is B's daughter. How is B related to A?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -3341,18 +3341,18 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3392,336 +3392,336 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
+          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>Daughter</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Priya herself</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>She is referring to herself.</t>
+          <t>Sister of husband → sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>A is also D’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M is the grandmother of O.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
+          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>N is M’s brother, so he is P’s maternal uncle.</t>
+          <t>Meera is Ravi’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>T is K’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>T’s sister is V → U is her nephew → V is aunt.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Father’s daughter is Lata herself → boy is her son.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3731,47 +3731,47 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>R is T’s grandfather through M.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3781,187 +3781,187 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
+          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Z is X’s uncle as he is Y’s brother.</t>
+          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
+          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Mother’s sister’s husband is uncle.</t>
+          <t>A is C’s sister.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3971,49 +3971,49 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Arjun is Kiran’s father.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -4026,133 +4026,133 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Z is X’s child.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>A is C’s son.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4192,186 +4192,186 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>R is S’s brother → T’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
+          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>Grandfather</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ravi is Tina’s uncle.</t>
+          <t>R is P’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>P is R’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Both are parents-in-law of a married couple.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>P is Q’s brother → R’s maternal uncle.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>The man is the brother of Suman’s husband → he is uncle.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>

--- a/Data/BloodRelation.xlsx
+++ b/Data/BloodRelation.xlsx
@@ -472,131 +472,131 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Granddaughter</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Daughter</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
+          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The man is the brother of Suman’s husband → he is uncle.</t>
+          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
+          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P is Q’s brother → R’s maternal uncle.</t>
+          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -626,112 +626,112 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>R is S’s brother → T’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ravi is Tina’s uncle.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,212 +741,212 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>R is T’s grandfather through M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Z is X’s child.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
+          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Z is X’s child.</t>
+          <t>A is also C’s son.</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1032,11 +1032,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
+          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1066,97 +1066,97 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Mother’s sister’s husband is uncle.</t>
+          <t>Ravi is Tina’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
+          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Z is X’s uncle as he is Y’s brother.</t>
+          <t>Arjun is Kiran’s father.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1166,19 +1166,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -1186,307 +1186,307 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>R is T’s grandfather through M.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>R is P’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Father’s daughter is Lata herself → boy is her son.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
+          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>N is M’s brother, so he is P’s maternal uncle.</t>
+          <t>T is K’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1496,23 +1496,23 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M is the grandmother of O.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1552,108 +1552,108 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
+          <t>A's father is B. C is B's sister. How is C related to A?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>She is referring to herself.</t>
+          <t>C is A’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>T’s sister is V → U is her nephew → V is aunt.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A's mother is B's daughter. How is B related to A?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -1661,18 +1661,18 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1712,91 +1712,91 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
+          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
+          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1806,19 +1806,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -1826,187 +1826,187 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Father’s sister’s son is a cousin.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Father’s sister’s son is a cousin.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2016,72 +2016,72 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Meena is Sneha’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
+          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
+          <t>Son’s mother is wife → her brother is brother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2091,112 +2091,112 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man is the brother of Suman’s husband → he is uncle.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Reena is Rahul’s mother too.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>G is the only daughter of H’s only son. How is G related to H?</t>
+          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Niece</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>Daughter</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Niece</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Granddaughter</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Only son’s daughter is granddaughter.</t>
+          <t>A is also D’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
+          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2226,257 +2226,257 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>F is D’s grandmother.</t>
+          <t>Meera is Ravi’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The man’s sister is Maya herself → he is her brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A's father is B. C is B's sister. How is C related to A?</t>
+          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C is A’s aunt.</t>
+          <t>P is Q’s brother → R’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Meena is Sneha’s mother-in-law.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2592,266 +2592,266 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>F is D’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
+          <t>G is the only daughter of H’s only son. How is G related to H?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>N’s sister is M → M is O’s sister-in-law.</t>
+          <t>Only son’s daughter is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Raj is Meena’s father.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
+          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2861,107 +2861,107 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C is A’s grandparent.</t>
+          <t>P is R’s brother as he is Q’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
+          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>S is Q’s grandfather.</t>
+          <t>N’s sister is M → M is O’s sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A is the son of B’s son. How is A related to B?</t>
+          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Nephew</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>Son</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Nephew</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Grandson</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>A is B’s grandson.</t>
+          <t>Father’s daughter is Lata herself → boy is her son.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2971,72 +2971,72 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>B is N’s brother → he is D’s maternal uncle.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
+          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Son’s mother is wife → her brother is brother-in-law.</t>
+          <t>Reena is Rahul’s mother too.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3061,77 +3061,77 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>A is C’s sister.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>B is N’s brother → he is D’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3141,157 +3141,157 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>N is M’s brother, so he is P’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
+          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P is R’s brother as he is Q’s maternal uncle.</t>
+          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
+          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>A is also C’s son.</t>
+          <t>Z is X’s uncle as he is Y’s brother.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3301,359 +3301,359 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L is M’s father.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A's mother is B's daughter. How is B related to A?</t>
+          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
+          <t>Sister of husband → sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>S is Q’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sister of husband → sister-in-law.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>A is also D’s daughter.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>A is C’s son.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Meera is Ravi’s grandmother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>T is K’s grandfather.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
+          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>T’s sister is V → U is her nephew → V is aunt.</t>
+          <t>M is the grandmother of O.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -3666,102 +3666,102 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>C is A’s grandparent.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3771,87 +3771,87 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Both are parents-in-law of a married couple.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
+          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3861,18 +3861,18 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
+          <t>L is M’s father.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3912,521 +3912,521 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>A is C’s sister.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
+          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Arjun is Kiran’s father.</t>
+          <t>P is R’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Raj is Meena’s father.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
+          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
+          <t>Mother’s sister’s husband is uncle.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
+          <t>A is the son of B’s son. How is A related to B?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>Grandson</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>Son</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A is C’s son.</t>
+          <t>A is B’s grandson.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>R is S’s brother → T’s uncle.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>R is P’s grandfather.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>P is R’s mother-in-law.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Both are parents-in-law of a married couple.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>She is referring to herself.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man’s sister is Maya herself → he is her brother.</t>
         </is>
       </c>
     </row>

--- a/Data/BloodRelation.xlsx
+++ b/Data/BloodRelation.xlsx
@@ -472,176 +472,176 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
+          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
+          <t>R is P’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
+          <t>Meena is Sneha’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -651,42 +651,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>R is S’s brother → T’s uncle.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>A's father is B. C is B's sister. How is C related to A?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -696,112 +696,112 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>C is A’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R is T’s grandfather through M.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -811,49 +811,49 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -866,93 +866,93 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
+          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Z is X’s child.</t>
+          <t>Son’s mother is wife → her brother is brother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
+          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grandfather</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A is also C’s son.</t>
+          <t>Raj is Meena’s father.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -992,96 +992,96 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
+          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ravi is Tina’s uncle.</t>
+          <t>Reena is Rahul’s mother too.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1091,108 +1091,108 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Arjun is Kiran’s father.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1232,127 +1232,127 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>R is P’s grandfather.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Father’s daughter is Lata herself → boy is her son.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1392,68 +1392,68 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Father</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Husband</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The man is the brother of Suman’s husband → he is uncle.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
+          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Grandfather</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -1461,72 +1461,72 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>T is K’s grandfather.</t>
+          <t>B is N’s brother → he is D’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man’s sister is Maya herself → he is her brother.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1536,79 +1536,79 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Mother’s sister’s husband is uncle.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A's father is B. C is B's sister. How is C related to A?</t>
+          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C is A’s aunt.</t>
+          <t>F is D’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Sister</t>
@@ -1616,27 +1616,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>T’s sister is V → U is her nephew → V is aunt.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A's mother is B's daughter. How is B related to A?</t>
+          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1646,19 +1646,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Grandmother</t>
@@ -1666,137 +1666,137 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
+          <t>Meera is Ravi’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>P is R’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
+          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
+          <t>Z is X’s uncle as he is Y’s brother.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
+          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Daughter</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Niece</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
+          <t>She is referring to herself.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1806,17 +1806,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1826,347 +1826,347 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
+          <t>A is the son of B’s son. How is A related to B?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Father’s sister’s son is a cousin.</t>
+          <t>A is B’s grandson.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Meena is Sneha’s mother-in-law.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
+          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Son’s mother is wife → her brother is brother-in-law.</t>
+          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The man is the brother of Suman’s husband → he is uncle.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>S is Q’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
+          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2176,202 +2176,202 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A is also D’s daughter.</t>
+          <t>A is C’s son.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Meera is Ravi’s grandmother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
+          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
+          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>R is S’s brother → T’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2381,62 +2381,62 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P is Q’s brother → R’s maternal uncle.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2486,19 +2486,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -2506,57 +2506,57 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2586,67 +2586,67 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>P is R’s brother as he is Q’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>F is D’s grandmother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>G is the only daughter of H’s only son. How is G related to H?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2656,122 +2656,122 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Only son’s daughter is granddaughter.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>R is T’s grandfather through M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2781,187 +2781,187 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>N’s sister is M → M is O’s sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
+          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Son</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P is R’s brother as he is Q’s maternal uncle.</t>
+          <t>Father’s sister’s son is a cousin.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
+          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>N’s sister is M → M is O’s sister-in-law.</t>
+          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Father’s daughter is Lata herself → boy is her son.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2976,27 +2976,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>T is K’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reena is Rahul’s mother too.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3046,14 +3046,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -3061,157 +3061,157 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>A is C’s sister.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
+          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>B is N’s brother → he is D’s maternal uncle.</t>
+          <t>Arjun is Kiran’s father.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>N is M’s brother, so he is P’s maternal uncle.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3221,27 +3221,27 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3251,32 +3251,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Z is X’s uncle as he is Y’s brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3286,19 +3286,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -3306,72 +3306,72 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
+          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sister of husband → sister-in-law.</t>
+          <t>P is Q’s brother → R’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
+          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3381,102 +3381,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>S is Q’s grandfather.</t>
+          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Sister of husband → sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Ravi is Tina’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
+          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3506,87 +3506,87 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>A is C’s son.</t>
+          <t>A is also C’s son.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>A is C’s sister.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>G is the only daughter of H’s only son. How is G related to H?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Only son’s daughter is granddaughter.</t>
         </is>
       </c>
     </row>
@@ -3632,367 +3632,367 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>T’s sister is V → U is her nephew → V is aunt.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
+          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>C is A’s grandparent.</t>
+          <t>L is M’s father.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Both are parents-in-law of a married couple.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
+          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L is M’s father.</t>
+          <t>Both are parents-in-law of a married couple.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>A is also D’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>P is R’s mother-in-law.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4032,51 +4032,51 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Raj is Meena’s father.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
+          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4086,14 +4086,14 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>Cousin</t>
@@ -4106,152 +4106,152 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Mother’s sister’s husband is uncle.</t>
+          <t>N is M’s brother, so he is P’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A is the son of B’s son. How is A related to B?</t>
+          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A is B’s grandson.</t>
+          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Niece</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Z is X’s child.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>A's mother is B's daughter. How is B related to A?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4261,172 +4261,172 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
+          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Grandparent</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Daughter</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>She is referring to herself.</t>
+          <t>C is A’s grandparent.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
+          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>The man’s sister is Maya herself → he is her brother.</t>
+          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
         </is>
       </c>
     </row>

--- a/Data/BloodRelation.xlsx
+++ b/Data/BloodRelation.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,192 +491,192 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R is P’s grandfather.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Meena is Sneha’s mother-in-law.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son or Daughter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Z is X’s child.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A's father is B. C is B's sister. How is C related to A?</t>
+          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -691,12 +691,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -706,462 +706,462 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C is A’s aunt.</t>
+          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>M is the grandmother of O.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Sister-in-law</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mother-in-law</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Co-mother-in-law</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Both are parents-in-law of a married couple.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
+          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Son’s mother is wife → her brother is brother-in-law.</t>
+          <t>Raj is Meena’s father.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meena is the daughter of Rani. Rani is the wife of Raj. How is Raj related to Meena?</t>
+          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Raj is Meena’s father.</t>
+          <t>P is R’s brother as he is Q’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>T is K’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
+          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reena is Rahul’s mother too.</t>
+          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>L is M’s father.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1171,87 +1171,87 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Sister of husband → sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1261,277 +1261,277 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>P is Q’s brother → R’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>A is C’s son.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
+          <t>A's mother is B's daughter. How is B related to A?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Father’s daughter is Lata herself → boy is her son.</t>
+          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>The man is the brother of Suman’s husband → he is uncle.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Brother</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>B is N’s brother → he is D’s maternal uncle.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The man’s sister is Maya herself → he is her brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1541,258 +1541,258 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Mother’s sister’s husband is uncle.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
+          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>F is D’s grandmother.</t>
+          <t>N is M’s brother, so he is P’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Ravi is Tina’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
+          <t>A says, 'B is my son’s mother’s brother.' How is B related to A?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Meera is Ravi’s grandmother.</t>
+          <t>Son’s mother is wife → her brother is brother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P is R’s mother-in-law.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Z is X’s uncle as he is Y’s brother.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Priya herself</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>She is referring to herself.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1832,91 +1832,91 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A is the son of B’s son. How is A related to B?</t>
+          <t>Pointing to a boy, Lata said, 'He is the son of my father's daughter.' Who is the boy?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Nephew</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>Son</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Nephew</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Grandson</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>A is B’s grandson.</t>
+          <t>Father’s daughter is Lata herself → boy is her son.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1946,354 +1946,354 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Father’s sister’s son is a cousin.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>N is the mother of D. B is the brother of N. How is B related to D?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>B is N’s brother → he is D’s maternal uncle.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sita is the sister of Ravi. Ravi is the father of Anjali. How is Sita related to Anjali?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sita is Ravi’s sister, and Ravi is Anjali’s father → Sita is Anjali’s aunt.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
+          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Father-in-law</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Grandfather</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>S is Q’s grandfather.</t>
+          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>If A is B’s brother and C is B’s father, what is A to C?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A is C’s son.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
+          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
+          <t>R is S’s brother → T’s uncle.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Cousin</t>
@@ -2301,77 +2301,77 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>R is T’s grandfather through M.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R is the brother of S. S is the father of T. How is R related to T?</t>
+          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Grandfather</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>R is S’s brother → T’s uncle.</t>
+          <t>A is also C’s son.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2381,22 +2381,22 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2406,19 +2406,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>Uncle</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Uncle</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Brother</t>
@@ -2426,62 +2426,62 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>If P is the daughter of Q and Q is the son of R, how is R related to P?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2491,77 +2491,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>R is P’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Ravi is the son of Sudha. Sudha is the daughter of Meera. How is Meera related to Ravi?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Meera is Ravi’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>If P is the maternal uncle of Q and Q is the daughter of R, how is P related to R?</t>
+          <t>Looking at a man, Suman said, 'His only brother is the father of my son.' Who is the man?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2571,112 +2571,112 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P is R’s brother as he is Q’s maternal uncle.</t>
+          <t>The man is the brother of Suman’s husband → he is uncle.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2706,147 +2706,147 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T is the daughter of M. M is the son of R. How is R related to T?</t>
+          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>R is T’s grandfather through M.</t>
+          <t>A is C’s sister.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister-in-law</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>N’s sister is M → M is O’s sister-in-law.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>M is N’s sister. O is N’s wife. What is M to O?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>N’s sister is M → M is O’s sister-in-law.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Looking at a photo, Raj says, 'He is the son of my father’s sister.' Who is the person?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2856,152 +2856,152 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Father’s sister’s son is a cousin.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A says, 'The girl in the photo is the daughter of the wife of my son.' Who is the girl?</t>
+          <t>Pointing to a man, Seema said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Wife of son is daughter-in-law → girl is granddaughter.</t>
+          <t>Mother’s husband is father → his only son is Seema’s brother.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T is the father of R. R is the mother of K. How is T related to K?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>T is K’s grandfather.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3011,87 +3011,87 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Brother</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>Wife</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3101,102 +3101,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Arjun is Kiran’s father.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>If X is the daughter of Y and Y is the brother of Z, how is Z related to X?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Z is X’s uncle as he is Y’s brother.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A is the father of B. B is the son of C. How is C related to A?</t>
+          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>If A is the father and B is the son of C, then C is A's wife.</t>
+          <t>Mother's husband is father. Only son of father is brother.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Reena is the mother of Kiran. Kiran is the sister of Rahul. Who is Reena to Rahul?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -3226,152 +3226,152 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Reena is Rahul’s mother too.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>C is A’s grandparent.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>D is the son of E. E is the daughter of F. How is F related to D?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>F is D’s grandmother.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>P is the brother of Q. Q is the mother of R. How is P related to R?</t>
+          <t>G is the only daughter of H’s only son. How is G related to H?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P is Q’s brother → R’s maternal uncle.</t>
+          <t>Only son’s daughter is granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>L is the wife of M. M is the son of N. How is N related to L?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Brother-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3381,32 +3381,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L’s husband is N’s son → N is L’s father-in-law.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>V is the sister of U. U is the husband of W. How is V related to W?</t>
+          <t>P is Q’s maternal grandmother. Q is the child of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3416,107 +3416,107 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sister of husband → sister-in-law.</t>
+          <t>P is R’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tina is the daughter of Ajay. Ajay is the brother of Ravi. How is Ravi related to Tina?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ravi is Tina’s uncle.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>If A is the brother of B and B is the daughter of C, then how is A related to C?</t>
+          <t>Q is the daughter of R. R is the son of S. How is S related to Q?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Grandfather</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>A is also C’s son.</t>
+          <t>S is Q’s grandfather.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A is the aunt of B. B is the daughter of C. How is A related to C?</t>
+          <t>Priya says, 'My father’s only daughter is the sister of my brother.' Who is Priya?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3526,47 +3526,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Priya herself</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>A is C’s sister.</t>
+          <t>She is referring to herself.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>G is the only daughter of H’s only son. How is G related to H?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3576,157 +3576,157 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Only son’s daughter is granddaughter.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>If M is the mother of N, and N is the father of O, what is M to O?</t>
+          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Aunt</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Grandmother</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Aunt</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M is the grandmother of O.</t>
+          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Sneha is married to Vishal. Vishal is the son of Meena. How is Meena related to Sneha?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mother-in-law</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Meena is Sneha’s mother-in-law.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>T’s sister is V → U is her nephew → V is aunt.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>K is the wife of L. M is the daughter of K. How is L related to M?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3736,197 +3736,197 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L is M’s father.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Introducing a man, a woman said, 'He is the only son of my mother's husband.' Who is the man?</t>
+          <t>U is the nephew of T. T has one sister V. How is V related to U?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mother's husband is father. Only son of father is brother.</t>
+          <t>T’s sister is V → U is her nephew → V is aunt.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>Kiran is the son of Nisha. Nisha is the wife of Arjun. How is Arjun related to Kiran?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>Arjun is Kiran’s father.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nina's daughter is the wife of Ajay's son. How is Nina related to Ajay?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sister-in-law</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mother-in-law</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Co-mother-in-law</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Both are parents-in-law of a married couple.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>K is the mother-in-law of P. R is the husband of K. How is R related to P?</t>
+          <t>A's father is B. C is B's sister. How is C related to A?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Father-in-law</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>R is K’s husband and father of P’s spouse → he is P’s father-in-law.</t>
+          <t>C is A’s aunt.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3936,162 +3936,162 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>A is also D’s daughter.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
+          <t>A is the son of B’s son. How is A related to B?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>The man's only sister's daughter’s mother is his wife.</t>
+          <t>A is B’s grandson.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
+          <t>Looking at a man, Arya says, 'He is the husband of the sister of my mother.' Who is the man?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>The only son of grandfather is the father. So, the man is her brother.</t>
+          <t>Mother’s sister’s husband is uncle.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>N is the brother of M. M is the mother of P. How is N related to P?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4101,157 +4101,157 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>N is M’s brother, so he is P’s maternal uncle.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B is the husband of C. A is the daughter of B. How is C related to A?</t>
+          <t>If A is the sister of B, B is the brother of C, and C is the son of D, how is A related to D?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Niece</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>Aunt</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Grandmother</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>C is A’s mother as she is B’s wife and B is A’s father.</t>
+          <t>A is also D’s daughter.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Looking at a man, Maya says, 'His sister is the daughter of my father.' Who is the man?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>The man’s sister is Maya herself → he is her brother.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>If X is the father of Y, and Y is the sister of Z, how is Z related to X?</t>
+          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Son or Daughter</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Z is X’s child.</t>
+          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A's mother is B's daughter. How is B related to A?</t>
+          <t>A is the father of B. B is the son of C. How is C related to A?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4261,18 +4261,18 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>If A’s mother is B’s daughter, B must be A’s grandmother.</t>
+          <t>If A is the father and B is the son of C, then C is A's wife.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4312,106 +4312,106 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>P is the mother of Q. Q is the sister of R. How is P related to R?</t>
+          <t>Pointing to a girl, Arun said, 'She is the only daughter of my mother’s son.' Who is the girl?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Cousin</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>If P is mother of Q and Q is sister of R, then P is also mother of R.</t>
+          <t>Mother’s son is Arun himself → the girl is his daughter.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>If A is the son of B and B is the daughter of C, how is C related to A?</t>
+          <t>Pointing to a man, Rita said, 'He is the son of my grandfather's only son.' Who is the man?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aunt</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Grandparent</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>C is A’s grandparent.</t>
+          <t>The only son of grandfather is the father. So, the man is her brother.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>If D is the daughter of E and E is the wife of F, how is D related to F?</t>
+          <t>Pointing to a photograph, a man says, 'She is the mother of my only sister's daughter.' Who is the woman?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Aunt</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>D is the daughter of E and E is F’s wife → D is F’s daughter.</t>
+          <t>The man's only sister's daughter’s mother is his wife.</t>
         </is>
       </c>
     </row>
